--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3260-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3260-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF1260C7-843B-45B9-A16F-E63232AF537A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D68CB153-6FDD-4FF2-ADA9-4BA73E9F9572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{073D74BE-E537-4398-98A1-F88604FF7956}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{19B1F6C2-7AC4-4962-944D-AC55454DB8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="3260-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1460,25 +1460,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF884C5E-64B8-4A0B-9DBB-32ACA017B207}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8933CE08-CEB2-437E-AC86-1E1939183493}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1632,7 +1632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2024</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2023</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2022</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>8.65</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2021</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2020</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2019</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2018</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>9.1300000000000008</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2017</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2016</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2015</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2014</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2013</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2012</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2011</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2010</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2009</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2008</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2007</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2006</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2005</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2004</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2003</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2002</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40" t="s">
         <v>38</v>
       </c>
